--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\ThermoBuzzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D606D89E-8C49-4202-8384-99B5625D3371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F90D474-EF92-4B00-B0D2-C0F558AE7A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3636" yWindow="1548" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>BOM</t>
   </si>
@@ -82,19 +82,40 @@
   </si>
   <si>
     <t>https://www.amazon.ca/ANALOG-DEVICES-TMP36-Temperature-Sensor/dp/B00JYQAIBM?source=ps-sl-shoppingads-lpcontext&amp;ref_=fplfs&amp;psc=1&amp;smid=AAEX2EKCSXB7D</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>NTC MF11</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>Arduino Nano (type)</t>
+  </si>
+  <si>
+    <t>Outlet with cabel?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,8 +138,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,97 +423,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="C4">
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\ThermoBuzzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F90D474-EF92-4B00-B0D2-C0F558AE7A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76CDC5D-D5C4-4E1E-B70E-46031212082A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3636" yWindow="1548" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>BOM</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Temperature Sensor</t>
   </si>
   <si>
-    <t>https://www.aliexpress.com/ssr/300000512/BundleDeals2?spm=a2g0o.productlist.main.11.4bad23b2W0Z283&amp;productIds=1005006982994037:12000038937173940&amp;pha_manifest=ssr&amp;_immersiveMode=true&amp;disableNav=YES&amp;sourceName=SEARCHProduct&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005006982994037%7C_p_origin_prod%3A1005007730203179&amp;pvid=fead97a0-7013-472f-8f48-f34087dd6ca8</t>
-  </si>
-  <si>
     <t>https://www.aliexpress.com/ssr/300000512/BundleDeals2?spm=a2g0o.productlist.main.12.4bad23b2W0Z283&amp;productIds=1005007345095808:12000040354473755&amp;pha_manifest=ssr&amp;_immersiveMode=true&amp;disableNav=YES&amp;sourceName=SEARCHProduct&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007345095808%7C_p_origin_prod%3A1005006953448721&amp;pvid=fead97a0-7013-472f-8f48-f34087dd6ca8</t>
   </si>
   <si>
@@ -87,9 +84,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>NTC MF11</t>
-  </si>
-  <si>
     <t>Battery</t>
   </si>
   <si>
@@ -97,13 +91,31 @@
   </si>
   <si>
     <t>Outlet with cabel?</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005004904865598.html?spm=a2g0o.productlist.main.2.44c36f379bcEWK&amp;algo_pvid=37a4732e-0e3b-49dc-90f7-42ef2dc8c721&amp;algo_exp_id=37a4732e-0e3b-49dc-90f7-42ef2dc8c721-23&amp;pdp_ext_f=%7B%22order%22%3A%2213720%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CAD%213.02%212.60%21%21%212.15%211.85%21%402101f70717742314163816448e5bdf%2112000030969396207%21sea%21CA%216218818596%21X%211%210%21n_tag%3A-29919%3Bd%3A26a99932%3Bm03_new_user%3A-29895&amp;curPageLogUid=BISAlr5fLDLJ&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005004904865598%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>NTC MF11, AHT20+BMP280</t>
+  </si>
+  <si>
+    <t>AHT20+BMP280 Temperature Humidity Air Pressure Module High-precision Digital Temperature Humidity and Air Pressure Sensor</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +128,20 @@
       <color rgb="FF333333"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="TT Norms Pro"/>
     </font>
   </fonts>
   <fills count="2">
@@ -135,16 +161,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -423,26 +454,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.88671875" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" customWidth="1"/>
     <col min="3" max="3" width="20.109375" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -451,47 +483,59 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4">
+        <v>2.19</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>13</v>
+      <c r="B5" t="s">
+        <v>25</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>3.99</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -499,42 +543,57 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
       <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H4" r:id="rId1" display="https://www.aliexpress.com/ssr/300000512/BundleDeals2?spm=a2g0o.productlist.main.12.4bad23b2W0Z283&amp;productIds=1005007345095808:12000040354473755&amp;pha_manifest=ssr&amp;_immersiveMode=true&amp;disableNav=YES&amp;sourceName=SEARCHProduct&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007345095808%7C_p_origin_prod%3A1005006953448721&amp;pvid=fead97a0-7013-472f-8f48-f34087dd6ca8" xr:uid="{8188D1EC-FE01-445E-8168-1909B737FBEE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\ThermoBuzzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76CDC5D-D5C4-4E1E-B70E-46031212082A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5D29E5-89FA-4AE7-9A49-68AA36311231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3636" yWindow="1548" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>BOM</t>
   </si>
@@ -90,9 +90,6 @@
     <t>Arduino Nano (type)</t>
   </si>
   <si>
-    <t>Outlet with cabel?</t>
-  </si>
-  <si>
     <t>https://www.aliexpress.com/item/1005004904865598.html?spm=a2g0o.productlist.main.2.44c36f379bcEWK&amp;algo_pvid=37a4732e-0e3b-49dc-90f7-42ef2dc8c721&amp;algo_exp_id=37a4732e-0e3b-49dc-90f7-42ef2dc8c721-23&amp;pdp_ext_f=%7B%22order%22%3A%2213720%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CAD%213.02%212.60%21%21%212.15%211.85%21%402101f70717742314163816448e5bdf%2112000030969396207%21sea%21CA%216218818596%21X%211%210%21n_tag%3A-29919%3Bd%3A26a99932%3Bm03_new_user%3A-29895&amp;curPageLogUid=BISAlr5fLDLJ&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005004904865598%7C_p_origin_prod%3A</t>
   </si>
   <si>
@@ -106,6 +103,15 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>9v dc</t>
+  </si>
+  <si>
+    <t>Battery socket</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/Duracell-Coppertop-Long-lasting-All-Purpose-Household/dp/B0014D0SL8/ref=asc_df_B0014D0SL8?mcid=c7225777934337b39c3f39a9df98d4c0&amp;tag=googleshopc0c-20&amp;linkCode=df0&amp;hvadid=706724917098&amp;hvpos=&amp;hvnetw=g&amp;hvrand=17738875034577000835&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9000685&amp;hvtargid=pla-568057207376&amp;hvocijid=17738875034577000835-B0014D0SL8-&amp;hvexpln=0&amp;gad_source=4&amp;th=1</t>
   </si>
 </sst>
 </file>
@@ -454,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.88671875" customWidth="1"/>
@@ -500,7 +506,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -509,7 +515,7 @@
         <v>2.19</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>11</v>
@@ -523,7 +529,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -543,7 +549,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
@@ -579,7 +585,7 @@
         <v>2.6</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -587,7 +593,18 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="E11">
+        <v>9.98</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\ThermoBuzzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5D29E5-89FA-4AE7-9A49-68AA36311231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B19955-0652-4A81-8482-612E6D368C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3636" yWindow="1548" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5520" yWindow="4152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>BOM</t>
   </si>
@@ -112,6 +112,18 @@
   </si>
   <si>
     <t>https://www.amazon.ca/Duracell-Coppertop-Long-lasting-All-Purpose-Household/dp/B0014D0SL8/ref=asc_df_B0014D0SL8?mcid=c7225777934337b39c3f39a9df98d4c0&amp;tag=googleshopc0c-20&amp;linkCode=df0&amp;hvadid=706724917098&amp;hvpos=&amp;hvnetw=g&amp;hvrand=17738875034577000835&amp;hvpone=&amp;hvptwo=&amp;hvqmt=&amp;hvdev=c&amp;hvdvcmdl=&amp;hvlocint=&amp;hvlocphy=9000685&amp;hvtargid=pla-568057207376&amp;hvocijid=17738875034577000835-B0014D0SL8-&amp;hvexpln=0&amp;gad_source=4&amp;th=1</t>
+  </si>
+  <si>
+    <t>Arduino pro mini</t>
+  </si>
+  <si>
+    <t>1PCS Pro mini Atmega328 Pro Mini 328 Mini ATMEGA328P 3.3V 8MHz 5V 16Mhz for Arduino Compatible Nano CP2102 FT232RL</t>
+  </si>
+  <si>
+    <t>Boost voltage regulator</t>
+  </si>
+  <si>
+    <t>Mini 0.8V-5V to 3V 3.3V 5V Boost Voltage Regulate Board Low-Power-Consumption High-Efficiency DC-DC Step-up Converter Module</t>
   </si>
 </sst>
 </file>
@@ -121,7 +133,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +161,13 @@
       <color rgb="FF000000"/>
       <name val="TT Norms Pro"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -171,7 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -179,6 +198,7 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -460,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.88671875" customWidth="1"/>
@@ -588,23 +608,45 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11">
-        <v>9.98</v>
-      </c>
-      <c r="F11" t="s">
-        <v>28</v>
+    <row r="10" spans="1:9">
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6.19</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12">
+        <v>9.98</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>3.3</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\ThermoBuzzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B19955-0652-4A81-8482-612E6D368C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC7E687-A9E2-4C6C-810B-1A5740683F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="4152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t>BOM</t>
   </si>
@@ -124,6 +135,102 @@
   </si>
   <si>
     <t>Mini 0.8V-5V to 3V 3.3V 5V Boost Voltage Regulate Board Low-Power-Consumption High-Efficiency DC-DC Step-up Converter Module</t>
+  </si>
+  <si>
+    <t>Product name</t>
+  </si>
+  <si>
+    <t>Product Description</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Total Price</t>
+  </si>
+  <si>
+    <t>Arduino Pro Mini</t>
+  </si>
+  <si>
+    <t> ATMEGA328P 3.3V 8MHz</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005009384358010.html?spm=a2g0o.detail.0.0.3d69kxh4kxh4TT&amp;mp=1&amp;pdp_npi=6%40dis%21CAD%21CAD+12.34%21CAD+6.19%21%21CAD+6.19%21%21%21%402101e2b217772431183538792e7ffd%2112000048937356319%21ct%21CA%216218818596%21%211%210%21</t>
+  </si>
+  <si>
+    <t>AA Battery</t>
+  </si>
+  <si>
+    <t>14500 Battery Box With Pins 1AA 1.5V</t>
+  </si>
+  <si>
+    <t>THT Battery Holder</t>
+  </si>
+  <si>
+    <t>AHT20+BMP280</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005005982427374.html?spm=a2g0o.detail.0.0.91dbOMYjOMYjR3&amp;mp=1&amp;sourceType=570&amp;pdp_npi=6%40dis%21CAD%21CAD+7.57%21CAD+4.59%21%21CAD+4.59%21%21%21%402101d6ff17773442520382830e94da%2112000035166631251%21ct%21CA%216218818596%21%211%210%21&amp;pdp_ext_f=%7B%22cart2PdpParams%22%3A%7B%22sourceType%22%3A%22570%22%2C%22cartSource%22%3A%22main%22%7D%7D</t>
+  </si>
+  <si>
+    <t>Shipping Fee</t>
+  </si>
+  <si>
+    <t>Scale up</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005006167931077.html?spm=a2g0o.detail.0.0.4a7cjdtRjdtRpQ&amp;mp=1&amp;pdp_npi=6%40dis%21CAD%21CAD+3.96%21CAD+3.86%21%21CAD+3.86%21%21%21%402101d6ff17773444964128610e94da%2112000036084126229%21ct%21CA%216218818596%21%211%210%21</t>
+  </si>
+  <si>
+    <t>0.8V-5V to 3V 3.3V 5V Boost Voltage Regulate</t>
+  </si>
+  <si>
+    <t>Thermisor</t>
+  </si>
+  <si>
+    <t>10PCS NTC Thermistor MF52 NTC-MF52AT</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005007016386078.html?spm=a2g0o.detail.0.0.177fzTz7zTz79e&amp;mp=1&amp;pdp_npi=6%40dis%21CAD%21CAD+7.07%21CAD+3.46%21%21CAD+3.46%21%21%21%402101d6ff17773445233621202e94da%2112000039082044667%21ct%21CA%216218818596%21%211%210%21</t>
+  </si>
+  <si>
+    <t>10PCS Passive Buzzer Kits 12085</t>
+  </si>
+  <si>
+    <t>Passive Buzzer</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005007038458518.html?spm=a2g0o.detail.0.0.291d6UQD6UQDcn&amp;mp=1&amp;sourceType=570&amp;pdp_npi=6%40dis%21CAD%21CAD+7.56%21CAD+3.09%21%21CAD+3.09%21%21%21%402101d6ff17773446457813771e94da%2112000039180355191%21ct%21CA%216218818596%21%211%210%21&amp;pdp_ext_f=%7B%22cart2PdpParams%22%3A%7B%22sourceType%22%3A%22570%22%2C%22cartSource%22%3A%22main%22%7D%7D</t>
+  </si>
+  <si>
+    <t>Buttons</t>
+  </si>
+  <si>
+    <t>m3 screw</t>
+  </si>
+  <si>
+    <t>resistor?</t>
+  </si>
+  <si>
+    <t>head pins</t>
+  </si>
+  <si>
+    <t>5 male 5 female</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005007235591794.html?spm=a2g0o.cart.0.0.31e138dackOqlz&amp;mp=1&amp;sourceType=570&amp;pdp_npi=6%40dis%21CAD%21CAD+16.72%21CAD+5.19%21%21CAD+5.19%21%21%21%402103119c17773470443845760e9623%2112000039908542823%21ct%21CA%216218818596%21%211%210%21&amp;pdp_ext_f=%7B%22cart2PdpParams%22%3A%7B%22sourceType%22%3A%22570%22%2C%22cartSource%22%3A%22main%22%7D%7D</t>
+  </si>
+  <si>
+    <t>6*6*10mm 20pics</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005006046180384.html?spm=a2g0o.cart.0.0.31e138dackOqlz&amp;mp=1&amp;pdp_npi=6%40dis%21CAD%21CAD+2.29%21CAD+2.29%21%21CAD+2.29%21%21%21%402103119c17773470443845760e9623%2112000035472972539%21ct%21CA%216218818596%21%211%210%21</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -133,7 +240,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +275,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -190,7 +305,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -199,6 +314,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -480,12 +596,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.21875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
     <col min="6" max="6" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -649,10 +766,238 @@
         <v>32</v>
       </c>
     </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>6.14</v>
+      </c>
+      <c r="F18" s="2">
+        <f>C18*D18</f>
+        <v>6.14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2">
+        <v>4.59</v>
+      </c>
+      <c r="F19" s="2">
+        <f>C19*D19</f>
+        <v>4.59</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>3.46</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" ref="F20:F27" si="0">C20*D20</f>
+        <v>3.46</v>
+      </c>
+      <c r="G20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>3.09</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="0"/>
+        <v>3.09</v>
+      </c>
+      <c r="G21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>2.29</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2.29</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>0.33</v>
+      </c>
+      <c r="E26">
+        <v>7.23</v>
+      </c>
+      <c r="F26" s="2">
+        <f>C26*D26+E26</f>
+        <v>7.5600000000000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>3.86</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="0"/>
+        <v>3.86</v>
+      </c>
+      <c r="G27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>5.19</v>
+      </c>
+      <c r="F32">
+        <f>D32</f>
+        <v>5.19</v>
+      </c>
+      <c r="G32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="2">
+        <f>SUM(F18:F32)</f>
+        <v>36.18</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H4" r:id="rId1" display="https://www.aliexpress.com/ssr/300000512/BundleDeals2?spm=a2g0o.productlist.main.12.4bad23b2W0Z283&amp;productIds=1005007345095808:12000040354473755&amp;pha_manifest=ssr&amp;_immersiveMode=true&amp;disableNav=YES&amp;sourceName=SEARCHProduct&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007345095808%7C_p_origin_prod%3A1005006953448721&amp;pvid=fead97a0-7013-472f-8f48-f34087dd6ca8" xr:uid="{8188D1EC-FE01-445E-8168-1909B737FBEE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\ThermoBuzzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC7E687-A9E2-4C6C-810B-1A5740683F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3230DF25-6BC2-4714-B659-4A6200472906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
   <si>
     <t>BOM</t>
   </si>
@@ -179,9 +179,6 @@
     <t>Shipping Fee</t>
   </si>
   <si>
-    <t>Scale up</t>
-  </si>
-  <si>
     <t>https://www.aliexpress.com/item/1005006167931077.html?spm=a2g0o.detail.0.0.4a7cjdtRjdtRpQ&amp;mp=1&amp;pdp_npi=6%40dis%21CAD%21CAD+3.96%21CAD+3.86%21%21CAD+3.86%21%21%21%402101d6ff17773444964128610e94da%2112000036084126229%21ct%21CA%216218818596%21%211%210%21</t>
   </si>
   <si>
@@ -209,12 +206,6 @@
     <t>Buttons</t>
   </si>
   <si>
-    <t>m3 screw</t>
-  </si>
-  <si>
-    <t>resistor?</t>
-  </si>
-  <si>
     <t>head pins</t>
   </si>
   <si>
@@ -231,6 +222,42 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Ultrasonic sensor</t>
+  </si>
+  <si>
+    <t>HC-SR04 3.3-5VNew version</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005005467178145.html?spm=a2g0o.productlist.main.2.48981450ohptjN&amp;algo_pvid=74ad5a5d-34d5-4956-b985-ef5a75be59a3&amp;algo_exp_id=74ad5a5d-34d5-4956-b985-ef5a75be59a3-1&amp;pdp_ext_f=%7B%22order%22%3A%2210615%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CAD%212.71%212.71%21%21%211.94%211.94%21%40210328df17774096350383208e9e52%2112000033197296308%21sea%21CA%216218818596%21X%211%210%21n_tag%3A-29919%3Bd%3A26a99932%3Bm03_new_user%3A-29895&amp;curPageLogUid=PazbM33tgsR5&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005005467178145%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>m3 self-tapping screw</t>
+  </si>
+  <si>
+    <t>ZONSANTA M3x50pc 5mm</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/4000982209705.html?spm=a2g0o.productlist.main.2.5e0a5049GO2c6k&amp;algo_pvid=d9d1041d-5b82-4d1d-adb8-2c50ae22e721&amp;algo_exp_id=d9d1041d-5b82-4d1d-adb8-2c50ae22e721-1&amp;pdp_ext_f=%7B%22order%22%3A%2214058%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CAD%212.04%211.99%21%21%211.46%211.42%21%40210328d417774091351247794e1c13%2110000013191635027%21sea%21CA%216218818596%21X%211%210%21n_tag%3A-29919%3Bd%3A26a99932%3Bm03_new_user%3A-29895&amp;curPageLogUid=Y5TAugc4ns7L&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A4000982209705%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005005620966310.html?spm=a2g0o.cart.0.0.358a38dadNcuNR&amp;mp=1&amp;pdp_npi=6%40dis%21CAD%21CAD+0.38%21CAD+0.32%21%21CAD+0.32%21%21%21%402101eee917774109006605329ec0dc%2112000033776650718%21ct%21CA%216218818596%21%215%210%21</t>
+  </si>
+  <si>
+    <t>GarageGuarde</t>
+  </si>
+  <si>
+    <t>Voltage Regulator</t>
+  </si>
+  <si>
+    <t>resistor</t>
+  </si>
+  <si>
+    <t>100k</t>
+  </si>
+  <si>
+    <t>10k</t>
   </si>
 </sst>
 </file>
@@ -596,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -833,10 +860,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
         <v>50</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -845,40 +872,40 @@
         <v>3.46</v>
       </c>
       <c r="F20" s="2">
-        <f t="shared" ref="F20:F27" si="0">C20*D20</f>
+        <f t="shared" ref="F20:F33" si="0">C20*D20</f>
         <v>3.46</v>
       </c>
       <c r="G20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>3.09</v>
+        <v>2.79</v>
       </c>
       <c r="F21" s="2">
         <f t="shared" si="0"/>
-        <v>3.09</v>
+        <v>2.79</v>
       </c>
       <c r="G21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -890,7 +917,7 @@
         <v>2.29</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -925,72 +952,303 @@
         <v>0.33</v>
       </c>
       <c r="E26">
-        <v>7.23</v>
+        <v>7.48</v>
       </c>
       <c r="F26" s="2">
         <f>C26*D26+E26</f>
-        <v>7.5600000000000005</v>
+        <v>7.8100000000000005</v>
+      </c>
+      <c r="G26" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="F27" s="2">
         <f t="shared" si="0"/>
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="F28" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="F29" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>2.79</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="0"/>
+        <v>2.79</v>
+      </c>
+      <c r="G30" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
         <v>5.19</v>
       </c>
-      <c r="F32">
-        <f>D32</f>
+      <c r="F33" s="2">
+        <f t="shared" si="0"/>
         <v>5.19</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
+      <c r="F35" s="2">
+        <f>SUM(F18:F33)</f>
+        <v>38.909999999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>2.71</v>
+      </c>
+      <c r="F38">
+        <f>D38*C38</f>
+        <v>2.71</v>
+      </c>
+      <c r="G38" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="2">
-        <f>SUM(F18:F32)</f>
-        <v>36.18</v>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <f>D39*C39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>6.14</v>
+      </c>
+      <c r="F41" s="2">
+        <f>C41*D41</f>
+        <v>6.14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>0.33</v>
+      </c>
+      <c r="E43" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="2">
+        <f>C43*D43</f>
+        <v>0.33</v>
+      </c>
+      <c r="G43" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>3.85</v>
+      </c>
+      <c r="F44" s="2">
+        <f>C44*D44</f>
+        <v>3.85</v>
+      </c>
+      <c r="G44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <f t="shared" ref="F46" si="1">C46*D46</f>
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="6:6">
+      <c r="F49" s="2">
+        <f>F35+SUM(F38:F46)</f>
+        <v>51.94</v>
       </c>
     </row>
   </sheetData>
